--- a/Mau_Import_DanhSachAn.xlsx
+++ b/Mau_Import_DanhSachAn.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -484,9 +484,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -522,187 +520,240 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2. Cách hệ thống nhận diện vụ trùng để KHÔNG import lại</t>
+          <t>1b. Import án nguồn từ NGOÀI hệ thống (chưa có Mã vụ) — cách nhóm nhiều bị can của cùng 1 vụ</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>• Sau khi tải file lên, hệ thống lấy toàn bộ vụ án đang có trong CSDL ra đối chiếu theo thứ tự ưu tiên: (1) trùng "Mã vụ" (so với cả Mã ngành cấp lẫn Mã nội sinh đã có) → (2) nếu mã không trùng, so tiếp theo cặp "Số QĐ KTVA" + "Ngày QĐ KTVA".</t>
+          <t>• Để TRỐNG cột "Mã vụ" (cột A) cho các vụ này — hệ thống sẽ tự cấp 1 mã hệ thống mới (giống hệt cách cấp mã khi tạo vụ án thủ công qua "Thêm vụ án").</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>• Vụ bị coi là trùng sẽ KHÔNG được ghi vào hệ thống (tránh ghi đè/xung đột dữ liệu đang có) — bảng xem trước sau khi tải file lên sẽ liệt kê rõ vụ nào bị coi là trùng và lý do, trước khi bấm nút ghi vào hệ thống.</t>
+          <t>• Khi Mã vụ để trống, hệ thống nhóm các dòng thuộc CÙNG 1 vụ theo cặp "Số QĐ KTVA" + "Ngày QĐ KTVA" GIỐNG HỆT NHAU — tức nhiều dòng có cùng Số/Ngày QĐ KTVA sẽ được hiểu là NHIỀU BỊ CAN của CÙNG 1 vụ, đúng như quy tắc "1 dòng = 1 bị can, vụ nhiều bị can lặp lại nhiều dòng" ở mục 1. Vì vậy Số QĐ KTVA/Ngày QĐ KTVA BẮT BUỘC phải điền và điền ĐÚNG Y HỆT nhau trên mọi dòng bị can của cùng 1 vụ (kể cả khoảng trắng thừa cũng có thể làm sai lệch — nên copy/paste thay vì gõ lại).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>• Chỉ những vụ THẬT SỰ MỚI (không trùng theo cả 2 tiêu chí trên) mới được ghi vào hệ thống. Vụ mới sẽ được cấp 1 mã hệ thống riêng (giống hệt tạo tay qua "Thêm vụ án"), còn "Mã vụ" trong file được giữ lại làm mã tham chiếu (Mã ngành cấp).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+          <t>• Có thể trộn lẫn trong cùng 1 file: dòng có Mã vụ (vụ đã có mã) và dòng không có Mã vụ (vụ nguồn ngoài) — hệ thống xử lý đúng cho từng loại theo quy tắc tương ứng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>3. Cột "Giai đoạn" / "Trạng thái" / "Nguồn" — gõ ĐÚNG 1 trong các giá trị sau (không phân biệt hoa/thường, nhưng phải đúng chữ, không viết tắt)</t>
+          <t>1c. Chỉ cần 3 cột là đủ để import — bổ sung phần còn thiếu sau</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>• Giai đoạn: Điều tra / Truy tố / Xét xử.</t>
+          <t>• BẮT BUỘC tối thiểu: "Số QĐ KTVA", "Ngày QĐ KTVA", "KSV chính". Thiếu 1 trong 3 cột này thì dòng đó rơi vào nhóm "vụ thiếu dữ liệu" và KHÔNG được import.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>• Trạng thái: Đang giải quyết / Đã xét xử / Chuyển đi / Tạm đình chỉ / Đình chỉ / Án huỷ.</t>
+          <t>• MỌI cột khác (Tên vụ, Giai đoạn, Trạng thái, Nguồn, ĐTV/CBĐT, Điều luật, Hạn ĐT vụ, và toàn bộ cột bị can) đều để trống được — dùng khi chỉ có thông tin sơ bộ lúc nhập nhanh, sẽ bổ sung dần sau.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>• Nguồn: Án khởi tố mới / Tin báo khởi tố lên / Án nơi khác chuyển đến / Phục hồi điều tra.</t>
+          <t>• Tên vụ để trống: hệ thống tự đặt tên tạm theo tên bị can đầu tiên (VD "Nguyễn Văn A và đồng phạm") nếu có khai bị can trên dòng đó; nếu dòng đó cũng chưa có bị can nào thì tên vụ để trống thật ("(chưa đặt tên)" khi xem trong hệ thống).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>• Nếu để trống hoặc gõ sai, hệ thống mặc định: Giai đoạn = Điều tra, Trạng thái = Đang giải quyết, Nguồn = Án khởi tố mới — và sẽ cảnh báo trên bảng xem trước để anh kiểm tra lại (không chặn import, chỉ nhắc).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
+          <t>• Sau khi import, mở lại vụ đó (Danh sách vụ án, hoặc màn Giao nhận hồ sơ khi thực tế cầm hồ sơ) → bấm "Sửa thông tin vụ án"/"✎ Sửa thông tin vụ án" để bổ sung dần các trường còn thiếu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>4. Cột "Ngày quyết định" / "Số quyết định"</t>
+          <t>2. Cách hệ thống nhận diện vụ trùng để KHÔNG import lại</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>• CHỈ bắt buộc điền khi cột Trạng thái KHÁC "Đang giải quyết" (tức vụ đã có kết quả: đã xét xử, tạm đình chỉ, đình chỉ, đã chuyển đi, án huỷ) — đây là ngày/số của quyết định kết thúc đó (bản án, QĐ tạm đình chỉ, QĐ đình chỉ...), KHÁC với Ngày/Số QĐ KTVA (quyết định khởi tố ban đầu).</t>
+          <t>• Sau khi tải file lên, hệ thống lấy toàn bộ vụ án đang có trong CSDL ra đối chiếu theo thứ tự ưu tiên: (1) trùng "Mã vụ" (so với cả Mã ngành cấp lẫn Mã nội sinh đã có) → (2) nếu mã không trùng, so tiếp theo cặp "Số QĐ KTVA" + "Ngày QĐ KTVA".</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>• Nếu Trạng thái là "Đang giải quyết" thì để trống 2 cột này.</t>
+          <t>• Vụ bị coi là trùng sẽ KHÔNG được ghi vào hệ thống (tránh ghi đè/xung đột dữ liệu đang có) — bảng xem trước sau khi tải file lên sẽ liệt kê rõ vụ nào bị coi là trùng và lý do, trước khi bấm nút ghi vào hệ thống.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>• Thiếu Ngày quyết định trong khi Trạng thái khác "Đang giải quyết" → dòng đó bị coi là LỖI, không được import (phải sửa lại file, tải lên lại).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
+          <t>• Chỉ những vụ THẬT SỰ MỚI (không trùng theo cả 2 tiêu chí trên) mới được ghi vào hệ thống. Vụ mới sẽ được cấp 1 mã hệ thống riêng (giống hệt tạo tay qua "Thêm vụ án"), còn "Mã vụ" trong file được giữ lại làm mã tham chiếu (Mã ngành cấp).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>5. Các cột ngày khác (Ngày QĐ KTVA, Hạn ĐT vụ, Hạn TG)</t>
+          <t>3. Cột "Giai đoạn" / "Trạng thái" / "Nguồn" — gõ ĐÚNG 1 trong các giá trị sau (không phân biệt hoa/thường, nhưng phải đúng chữ, không viết tắt)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>• Dùng định dạng ngày Excel bình thường (ô đã bôi định dạng Date), hoặc gõ text dạng dd.mm.yyyy / dd/mm/yyyy.</t>
+          <t>• Giai đoạn: Điều tra / Truy tố / Xét xử.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>• "Ngày QĐ KTVA" là BẮT BUỘC cho mọi dòng (dùng để sinh mã hệ thống + xác định vụ).</t>
+          <t>• Trạng thái: Đang giải quyết / Đã xét xử / Chuyển đi / Tạm đình chỉ / Đình chỉ / Án huỷ.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>• "Hạn TG" (hạn tạm giam) chỉ điền khi bị can đang tạm giam; để trống nghĩa là tại ngoại — hệ thống suy ra cột "Biện pháp" từ đây nếu cột đó cũng bỏ trống.</t>
+          <t>• Nguồn: Án khởi tố mới / Tin báo khởi tố lên / Án nơi khác chuyển đến / Phục hồi điều tra.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6. Cột "Biện pháp" (ngăn chặn) / "Đảng viên" (bị can)</t>
-        </is>
-      </c>
-    </row>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>• Nếu để trống hoặc gõ sai, hệ thống mặc định: Giai đoạn = Điều tra, Trạng thái = Đang giải quyết, Nguồn = Án khởi tố mới — và sẽ cảnh báo trên bảng xem trước để anh kiểm tra lại (không chặn import, chỉ nhắc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>• Biện pháp: gõ "Tạm giam" hoặc "Tại ngoại". Nếu để trống, hệ thống tự suy ra: có "Hạn TG" → Tạm giam, không có → Tại ngoại.</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>4. Cột "Ngày quyết định" / "Số quyết định"</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>• Đảng viên: gõ bất kỳ ký tự gì (VD "x") để đánh dấu CÓ, để trống nghĩa là KHÔNG.</t>
+          <t>• CHỈ bắt buộc điền khi cột Trạng thái KHÁC "Đang giải quyết" (tức vụ đã có kết quả: đã xét xử, tạm đình chỉ, đình chỉ, đã chuyển đi, án huỷ) — đây là ngày/số của quyết định kết thúc đó (bản án, QĐ tạm đình chỉ, QĐ đình chỉ...), KHÁC với Ngày/Số QĐ KTVA (quyết định khởi tố ban đầu).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7. Sau khi điền xong</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>• Xoá dòng ví dụ (dòng 2-3, tô vàng) trước khi dùng file thật, hoặc ghi đè thành dữ liệu thật đầu tiên.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>• Nếu Trạng thái là "Đang giải quyết" thì để trống 2 cột này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>• Thiếu Ngày quyết định trong khi Trạng thái khác "Đang giải quyết" → KHÔNG còn bị chặn (2026-07-13, do dữ liệu nguồn cũ hay thiếu khoản này) — hệ thống tự tạm dùng NGÀY ƯỚC TÍNH = Ngày QĐ KTVA + 4 tháng, và tự ghi rõ vào ô "Ghi chú" của vụ (kèm cảnh báo ⚠) để nhắc cập nhật lại ngày thật sau. Bảng xem trước cũng liệt kê rõ dòng nào đang dùng ngày ước tính này để dễ theo dõi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1"/>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>• Mở qlva.html → đăng nhập → vào module "Import Excel" → tải file này lên → hệ thống tự đối chiếu và hiện bảng xem trước 3 nhóm: vụ mới / vụ trùng (bỏ qua) / vụ thiếu dữ liệu (bỏ qua) → kiểm tra kỹ nhóm "vụ mới" → bấm "Ghi ... vụ mới vào hệ thống" → chọn kỳ báo cáo để tính các vụ mới này vào (hoặc chọn "Kỳ lưu trữ án cũ" nếu đây là án cũ nhập lại cho đủ hồ sơ, không phải án mới phát sinh trong kỳ đang làm việc) → xác nhận.</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>5. Các cột ngày khác (Ngày QĐ KTVA, Hạn ĐT vụ, Hạn TG)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>• Dùng định dạng ngày Excel bình thường (ô đã bôi định dạng Date), hoặc gõ text dạng dd.mm.yyyy / dd/mm/yyyy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>• "Ngày QĐ KTVA" là BẮT BUỘC cho mọi dòng (dùng để sinh mã hệ thống + xác định vụ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>• "Hạn TG" (hạn tạm giam) chỉ điền khi bị can đang tạm giam; để trống nghĩa là tại ngoại — hệ thống suy ra cột "Biện pháp" từ đây nếu cột đó cũng bỏ trống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>6. Cột "Biện pháp" (ngăn chặn) / "Đảng viên" (bị can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>• Biện pháp: gõ "Tạm giam" hoặc "Tại ngoại". Nếu để trống, hệ thống tự suy ra: có "Hạn TG" → Tạm giam, không có → Tại ngoại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>• Đảng viên: gõ bất kỳ ký tự gì (VD "x") để đánh dấu CÓ, để trống nghĩa là KHÔNG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>7. Sau khi điền xong</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>• Xoá dòng ví dụ (dòng 2-3, tô vàng) trước khi dùng file thật, hoặc ghi đè thành dữ liệu thật đầu tiên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>• Mở qlva.html → đăng nhập → vào module "Import Excel" → tải file này lên → hệ thống tự đối chiếu và hiện bảng xem trước 3 nhóm: vụ mới / vụ trùng (bỏ qua) / vụ thiếu dữ liệu (bỏ qua) → kiểm tra kỹ nhóm "vụ mới" → bấm "Ghi ... vụ mới vào hệ thống" → chọn kỳ báo cáo để tính các vụ mới này vào (hoặc chọn "Kỳ lưu trữ án cũ" nếu đây là án cũ nhập lại cho đủ hồ sơ, không phải án mới phát sinh trong kỳ đang làm việc) → xác nhận.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>• Khác với cách import cũ, mẫu này khiến hệ thống tự ghi đầy đủ nhật ký (Khởi tố vụ, Khởi tố bị can, và Hoàn thành nếu vụ đã có kết quả) ngay khi import — không cần chạy thêm công cụ "Dựng lại lịch sử" cho những vụ vừa nhập bằng file này.</t>
         </is>

--- a/Mau_Import_DanhSachAn.xlsx
+++ b/Mau_Import_DanhSachAn.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -520,7 +519,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -549,7 +547,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -585,7 +582,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -614,7 +610,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -650,7 +645,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
@@ -708,7 +702,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
@@ -734,26 +727,62 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>7. Sau khi điền xong</t>
+          <t>6b. Cột "Tội danh" (bị can) — cách ghi để "Mã ĐL" (điều luật) tự nhận đúng NGAY khi import, không cần chạy lại "Chuẩn hóa" sau</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>• Xoá dòng ví dụ (dòng 2-3, tô vàng) trước khi dùng file thật, hoặc ghi đè thành dữ liệu thật đầu tiên.</t>
+          <t>• Ghi ĐÚNG 1 trong 2 cách: (1) tên tội danh đầy đủ giống trong danh mục hệ thống (VD "Tội trộm cắp tài sản" — có/không tiền tố "Tội " đều được, không phân biệt hoa/thường), hoặc (2) CHỈ ghi số điều luật (VD "173").</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>• Mở qlva.html → đăng nhập → vào module "Import Excel" → tải file này lên → hệ thống tự đối chiếu và hiện bảng xem trước 3 nhóm: vụ mới / vụ trùng (bỏ qua) / vụ thiếu dữ liệu (bỏ qua) → kiểm tra kỹ nhóm "vụ mới" → bấm "Ghi ... vụ mới vào hệ thống" → chọn kỳ báo cáo để tính các vụ mới này vào (hoặc chọn "Kỳ lưu trữ án cũ" nếu đây là án cũ nhập lại cho đủ hồ sơ, không phải án mới phát sinh trong kỳ đang làm việc) → xác nhận.</t>
+          <t>• KHÔNG ghi kèm số điều trong ngoặc sau tên (VD "Tội trộm cắp tài sản (Điều 173)") — dạng này KHÔNG khớp được danh mục, cột "Mã ĐL" ở Biểu B10 sẽ vẫn hiện "chưa xác định" dù cột "Điều luật" cấp vụ đã có giá trị.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>• Nếu để trống hoàn toàn, hệ thống tự suy tội danh chính từ cột "Điều luật" cấp vụ (áp dụng chung cho MỌI bị can của vụ đó) — chỉ nên dùng cho vụ đồng phạm cùng 1 tội; vụ nhiều tội danh khác nhau theo từng bị can thì nên ghi rõ cột này cho từng người.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>• Vụ 1 bị can nhiều tội danh: mẫu này chỉ hỗ trợ 1 tội danh/dòng — bổ sung các tội còn lại sau qua "Sửa thông tin vụ án"/nút "Sửa" ở dòng bị can đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>7. Sau khi điền xong</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>• Xoá dòng ví dụ (dòng 2-3, tô vàng) trước khi dùng file thật, hoặc ghi đè thành dữ liệu thật đầu tiên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>• Mở qlva.html → đăng nhập → vào module "Import Excel" → tải file này lên → hệ thống tự đối chiếu và hiện bảng xem trước 3 nhóm: vụ mới / vụ trùng (bỏ qua) / vụ thiếu dữ liệu (bỏ qua) → kiểm tra kỹ nhóm "vụ mới" → bấm "Ghi ... vụ mới vào hệ thống" → chọn kỳ báo cáo để tính các vụ mới này vào (hoặc chọn "Kỳ lưu trữ án cũ" nếu đây là án cũ nhập lại cho đủ hồ sơ, không phải án mới phát sinh trong kỳ đang làm việc) → xác nhận.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>• Khác với cách import cũ, mẫu này khiến hệ thống tự ghi đầy đủ nhật ký (Khởi tố vụ, Khởi tố bị can, và Hoàn thành nếu vụ đã có kết quả) ngay khi import — không cần chạy thêm công cụ "Dựng lại lịch sử" cho những vụ vừa nhập bằng file này.</t>
         </is>
@@ -1001,7 +1030,7 @@
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>Tội cướp tài sản (Điều 168 BLHS)</t>
+          <t>Tội cướp tài sản</t>
         </is>
       </c>
       <c r="U2" s="5" t="inlineStr">
@@ -1102,7 +1131,7 @@
       </c>
       <c r="T3" s="6" t="inlineStr">
         <is>
-          <t>Tội cướp tài sản (Điều 168 BLHS)</t>
+          <t>Tội cướp tài sản</t>
         </is>
       </c>
       <c r="U3" s="6" t="inlineStr">
